--- a/college-posters/data/字段表_211第三批.xlsx
+++ b/college-posters/data/字段表_211第三批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,68 +505,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>金融与经济、传媒与互联网、医疗卫生与医药</t>
+          <t>石牌校区：广州主校区；番禺校区：大学城校区；珠海校区：海滨校区</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>暨南大学</t>
+          <t>上海大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>石牌校区：广州主校区；番禺校区：大学城校区；珠海校区：海滨校区</t>
+          <t>机械工程、材料科学与工程、计算机科学与技术、通信工程、美术学、新闻学</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>暨南大学</t>
+          <t>上海大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>宝山校区：泮池等江南园林景观；延长校区：静安区老校区；嘉定校区：新建校区</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>上海大学</t>
+          <t>西南大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>机械工程、材料科学与工程、计算机科学与技术、通信工程、美术学、新闻学</t>
+          <t>教育学、心理学、生物科学、汉语言文学、蚕学、农学</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,73 +588,73 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>上海大学</t>
+          <t>西南大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>上海先进制造、互联网与信息技术、文化传媒</t>
+          <t>缙云山：校园背靠缙云山；北碚校区：重庆主校区；荣昌校区：动物科学特色校区</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海大学</t>
+          <t>中国石油大学（北京）</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>宝山校区：泮池等江南园林景观；延长校区：静安区老校区；嘉定校区：新建校区</t>
+          <t>石油工程、资源勘查工程、化学工程与工艺、油气储运工程、勘查技术与工程、安全工程</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海大学</t>
+          <t>中国石油大学（北京）</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>昌平校区：军都山下主校区；克拉玛依校区：新疆校区；图书馆：昌平校区标志建筑</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>西南大学</t>
+          <t>河海大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>教育学、心理学、生物科学、汉语言文学、蚕学、农学</t>
+          <t>水利水电工程、港口航道与海岸工程、水文与水资源工程、土木工程、环境工程、农业水利工程</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,161 +676,161 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>西南大学</t>
+          <t>河海大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>教育与科研、农业与生物、党政机关与事业单位</t>
+          <t>西康路校区：清凉山下老校区；江宁校区：南京主校区；常州校区：新建校区</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>西南大学</t>
+          <t>陕西师范大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>软科中国大学排名</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>缙云山：校园背靠缙云山；北碚校区：重庆主校区；荣昌校区：动物科学特色校区</t>
+          <t>2026年第63名（与河海大学并列，来源为榜单样本）</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核（并列名次来自样本）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>西南大学</t>
+          <t>陕西师范大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>汉语言文学、历史学、教育学、心理学、数学与应用数学、地理科学</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（北京）</t>
+          <t>陕西师范大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>石油工程、资源勘查工程、化学工程与工艺、油气储运工程、勘查技术与工程、安全工程</t>
+          <t>雁塔校区：大雁塔旁老校区；长安校区：长安区主校区；图书馆：长安校区标志建筑</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（北京）</t>
+          <t>北京工业大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>石油石化央企、能源与化工、地质勘探</t>
+          <t>土木工程、建筑学、计算机科学与技术、电子信息工程、环境工程、机械工程</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（北京）</t>
+          <t>北京工业大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>昌平校区：军都山下主校区；克拉玛依校区：新疆校区；图书馆：昌平校区标志建筑</t>
+          <t>2024届本科深造率64.8%（知乎汇总文章）</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核（第三方单一来源）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中国石油大学（北京）</t>
+          <t>北京工业大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>平乐园校区：朝阳区主校区；奥运场馆：北工大体育馆；通州校区：城市副中心校区</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>河海大学</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>水利水电工程、港口航道与海岸工程、水文与水资源工程、土木工程、环境工程、农业水利工程</t>
+          <t>采矿工程、安全工程、矿物加工工程、测绘工程、土木工程、电气工程及其自动化</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -852,572 +852,110 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>河海大学</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>水利水电与电力、土木交通工程、环保与水务</t>
+          <t>南湖校区：徐州主校区；文昌校区：老校区；图书馆：南湖校区标志建筑</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>河海大学</t>
+          <t>西北大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>西康路校区：清凉山下老校区；江宁校区：南京主校区；常州校区：新建校区</t>
+          <t>考古学、地质学、汉语言文学、经济学、历史学、化学工程与工艺</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>河海大学</t>
+          <t>西北大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>太白校区：西安城内老校区；长安校区：长安区主校区；博物馆：考古学科特色展馆</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>陕西师范大学</t>
+          <t>云南大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>软科中国大学排名</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026年第63名（与河海大学并列，来源为榜单样本）</t>
+          <t>民族学、生态学、生物科学、汉语言文学、经济学、计算机科学与技术</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核（并列名次来自样本）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>陕西师范大学</t>
+          <t>云南大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>汉语言文学、历史学、教育学、心理学、数学与应用数学、地理科学</t>
+          <t>东陆校区：翠湖畔的老校区；银杏道：东陆校区秋季景观；呈贡校区：大学城主校区</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>陕西师范大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>教育与科研、党政机关与事业单位、文化传媒</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>陕西师范大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>雁塔校区：大雁塔旁老校区；长安校区：长安区主校区；图书馆：长安校区标志建筑</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>陕西师范大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>北京工业大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>土木工程、建筑学、计算机科学与技术、电子信息工程、环境工程、机械工程</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>北京工业大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>深造率</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2024届本科深造率64.8%（知乎汇总文章）</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核（第三方单一来源）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>北京工业大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>北京建设与城市运行、电子信息与互联网、先进制造</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>北京工业大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>平乐园校区：朝阳区主校区；奥运场馆：北工大体育馆；通州校区：城市副中心校区</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>北京工业大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>中国矿业大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>双一流2个：矿业工程、安全科学与工程（转载名单未区分徐州与北京校区）；办学117年</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>中国矿业大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>采矿工程、安全工程、矿物加工工程、测绘工程、土木工程、电气工程及其自动化</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>中国矿业大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>煤炭与能源央企、安全与应急管理、土木与测绘</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>中国矿业大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>南湖校区：徐州主校区；文昌校区：老校区；图书馆：南湖校区标志建筑</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>中国矿业大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>西北大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>考古学、地质学、汉语言文学、经济学、历史学、化学工程与工艺</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>西北大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>科研院所与文博、能源与地质、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>西北大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>太白校区：西安城内老校区；长安校区：长安区主校区；博物馆：考古学科特色展馆</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>西北大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>云南大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>民族学、生态学、生物科学、汉语言文学、经济学、计算机科学与技术</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>云南大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>党政机关与事业单位、生态环保与科研、教育与文化</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>云南大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>东陆校区：翠湖畔的老校区；银杏道：东陆校区秋季景观；呈贡校区：大学城主校区</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>云南大学</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -1981,9 +1519,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2106,12 +1644,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2739,9 +2277,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2402,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3497,9 +3035,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3160,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4255,9 +3793,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4380,12 +3918,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5013,9 +4551,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5138,12 +4676,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5771,9 +5309,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5896,12 +5434,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6529,9 +6067,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6192,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7287,9 +6825,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7412,12 +6950,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8045,9 +7583,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8170,12 +7708,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8104,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>双一流2个：矿业工程、安全科学与工程（转载名单未区分徐州与北京校区）；办学117年</t>
+          <t>双一流2个：矿业工程、安全科学与工程（徐州本部与北京校区分别列入，学科相同）；办学117年</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -8579,9 +8117,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -8803,9 +8341,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8928,12 +8466,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
